--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Credential" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="URL's" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Username</t>
   </si>
@@ -24,10 +24,70 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Kuchbhi@123</t>
-  </si>
-  <si>
-    <t>VIJAY</t>
+    <t>mis.admin.400021</t>
+  </si>
+  <si>
+    <t>NewSecure$Pssword123</t>
+  </si>
+  <si>
+    <t>web (FE)</t>
+  </si>
+  <si>
+    <t>iam</t>
+  </si>
+  <si>
+    <t>booking</t>
+  </si>
+  <si>
+    <t>lmfm</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>network</t>
+  </si>
+  <si>
+    <t>notification</t>
+  </si>
+  <si>
+    <t>driverapp (BFF)</t>
+  </si>
+  <si>
+    <t>scanning</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30000</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30081</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30082</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30083</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30084</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30085</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30086</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30087</t>
+  </si>
+  <si>
+    <t>http://10.10.130.123:30088</t>
+  </si>
+  <si>
+    <t>Franchise</t>
+  </si>
+  <si>
+    <t>https://apidev.omone.in</t>
   </si>
 </sst>
 </file>
@@ -372,13 +432,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -386,17 +448,26 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId1" display="Kuchbhi@123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -404,9 +475,90 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId2"/>
+    <hyperlink ref="C2" r:id="rId3"/>
+    <hyperlink ref="D2" r:id="rId4"/>
+    <hyperlink ref="E2" r:id="rId5"/>
+    <hyperlink ref="F2" r:id="rId6"/>
+    <hyperlink ref="G2" r:id="rId7"/>
+    <hyperlink ref="H2" r:id="rId8"/>
+    <hyperlink ref="I2" r:id="rId9"/>
+    <hyperlink ref="J2" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,113 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226" filterPrivacy="true"/>
   <sheets>
     <sheet name="Credential" sheetId="1" r:id="rId1"/>
     <sheet name="URL's" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="LMFM_Data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>mis.admin.400021</t>
-  </si>
-  <si>
-    <t>NewSecure$Pssword123</t>
-  </si>
-  <si>
-    <t>web (FE)</t>
-  </si>
-  <si>
-    <t>iam</t>
-  </si>
-  <si>
-    <t>booking</t>
-  </si>
-  <si>
-    <t>lmfm</t>
-  </si>
-  <si>
-    <t>mm</t>
-  </si>
-  <si>
-    <t>network</t>
-  </si>
-  <si>
-    <t>notification</t>
-  </si>
-  <si>
-    <t>driverapp (BFF)</t>
-  </si>
-  <si>
-    <t>scanning</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30000</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30081</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30082</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30083</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30084</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30085</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30086</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30087</t>
-  </si>
-  <si>
-    <t>http://10.10.130.123:30088</t>
-  </si>
-  <si>
-    <t>Franchise</t>
-  </si>
-  <si>
-    <t>https://apidev.omone.in</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,23 +63,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -222,6 +152,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -256,6 +187,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -290,20 +222,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -425,149 +353,244 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="27.85546875" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B2"/>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Username</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Password</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Vijay.kumar</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Vijay@123</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="Kuchbhi@123"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>web (FE)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>iam</v>
+      </c>
+      <c r="C1" t="str">
+        <v>booking</v>
+      </c>
+      <c r="D1" t="str">
+        <v>lmfm</v>
+      </c>
+      <c r="E1" t="str">
+        <v>mm</v>
+      </c>
+      <c r="F1" t="str">
+        <v>network</v>
+      </c>
+      <c r="G1" t="str">
+        <v>notification</v>
+      </c>
+      <c r="H1" t="str">
+        <v>driverapp (BFF)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>scanning</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Franchise</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>http://10.10.130.123:30000</v>
+      </c>
+      <c r="B2" t="str">
+        <v>https://apidev.omone.in</v>
+      </c>
+      <c r="C2" t="str">
+        <v>https://apidev.omone.in/atom-booking</v>
+      </c>
+      <c r="D2" t="str">
+        <v>https://apidev.omone.in/atom-lmfm</v>
+      </c>
+      <c r="E2" t="str">
+        <v>https://apidev.omone.in/atom-mm</v>
+      </c>
+      <c r="F2" t="str">
+        <v>https://apidev.omone.in/atom-network</v>
+      </c>
+      <c r="G2" t="str">
+        <v>https://apidev.omone.in</v>
+      </c>
+      <c r="H2" t="str">
+        <v>https://apidev.omone.in/atom-driverapp</v>
+      </c>
+      <c r="I2" t="str">
+        <v>https://apidev.omone.in/atom-scanning</v>
+      </c>
+      <c r="J2" t="str">
+        <v>https://apidev.omone.in</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="C2" r:id="rId3"/>
-    <hyperlink ref="D2" r:id="rId4"/>
-    <hyperlink ref="E2" r:id="rId5"/>
-    <hyperlink ref="F2" r:id="rId6"/>
-    <hyperlink ref="G2" r:id="rId7"/>
-    <hyperlink ref="H2" r:id="rId8"/>
-    <hyperlink ref="I2" r:id="rId9"/>
-    <hyperlink ref="J2" r:id="rId10"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>BranchCode</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ClusterId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ClusterName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>VehicleNo</v>
+      </c>
+      <c r="E1" t="str">
+        <v>VehicleType</v>
+      </c>
+      <c r="F1" t="str">
+        <v>VehicleCapacityKg</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2115</v>
+      </c>
+      <c r="B2">
+        <v>7552</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CLUSTER-400604</v>
+      </c>
+      <c r="D2" t="str">
+        <v>MH02DE1001</v>
+      </c>
+      <c r="E2" t="str">
+        <v>14FT</v>
+      </c>
+      <c r="F2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>803</v>
+      </c>
+      <c r="B3">
+        <v>20448</v>
+      </c>
+      <c r="C3" t="str">
+        <v>CLUSTER-803</v>
+      </c>
+      <c r="D3" t="str">
+        <v>MH02DE1002</v>
+      </c>
+      <c r="E3" t="str">
+        <v>14FT</v>
+      </c>
+      <c r="F3">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1001</v>
+      </c>
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CLUSTER-1001</v>
+      </c>
+      <c r="D4" t="str">
+        <v>MH02DE1003</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TATA-ACE</v>
+      </c>
+      <c r="F4">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
 </worksheet>
 </file>